--- a/output/pdf_financials_xlsx/BEW.xlsx
+++ b/output/pdf_financials_xlsx/BEW.xlsx
@@ -1679,7 +1679,7 @@
         <v>-1.971884</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.416521</v>
+        <v>-0.416521</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>2.085246</v>
@@ -1862,7 +1862,7 @@
         <v>-1.971884</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.416521</v>
+        <v>-0.416521</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>2.085246</v>
@@ -2491,7 +2491,7 @@
         <v>-28.0205181372478</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>4.8766812140158</v>
+        <v>-4.8766812140158</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>20.80066219101194</v>
@@ -6280,43 +6280,43 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.012582</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.023157</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.275835</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.275835</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.175145</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.793971</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.950833</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.312471</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.341807</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.349137</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.38161</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.9758019999999999</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>1.126163</v>
       </c>
     </row>
     <row r="93">
@@ -6676,7 +6676,7 @@
         <v>-0.211276</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.07241599999999999</v>
+        <v>-0.07241599999999999</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>-2.684813</v>
@@ -7820,16 +7820,16 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.24789</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.27113</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.017185</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.020084</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0.129865</v>
@@ -11346,7 +11346,11 @@
           <t>Share-based payment reserve (Note 15)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -13290,7 +13294,11 @@
           <t>Share-based payment reserve (Note 14)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -14146,7 +14154,11 @@
           <t>Share-based payment reserve (Note 14)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -14996,7 +15008,11 @@
           <t>Share-based payment reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -16368,7 +16384,11 @@
           <t>Reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -17436,7 +17456,11 @@
           <t>Reserve for warrants (Note 12)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -18822,7 +18846,11 @@
           <t>Reserves for warrants (note 9(c))</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -20416,7 +20444,11 @@
           <t>Reserves for warrants (note 9(c))</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -21570,7 +21602,11 @@
           <t>Reserves for warrants (note 10(c))</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -43840,10 +43876,10 @@
         </is>
       </c>
       <c r="M334" s="5" t="n">
-        <v>0.07241599999999999</v>
+        <v>-0.07241599999999999</v>
       </c>
       <c r="N334" s="5" t="n">
-        <v>2.684813</v>
+        <v>-2.684813</v>
       </c>
       <c r="O334" t="inlineStr">
         <is>
@@ -48958,7 +48994,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -52124,7 +52164,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -71534,7 +71578,7 @@
         <v>-1.971884</v>
       </c>
       <c r="S598" s="5" t="n">
-        <v>0.416521</v>
+        <v>-0.416521</v>
       </c>
       <c r="T598" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BEW.xlsx
+++ b/output/pdf_financials_xlsx/BEW.xlsx
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.325236</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00724</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.003043</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1113,22 +1113,22 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.025424</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.018743</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.008454</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.026811</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.1112</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.063321</v>
       </c>
     </row>
     <row r="13">
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-9.355484000000001</v>
+        <v>-9.680720000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.273834</v>
+        <v>-1.281074</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.193133</v>
@@ -2136,7 +2136,7 @@
         <v>-0.211276</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.041691</v>
+        <v>-0.044734</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-2.684813</v>
@@ -2148,22 +2148,22 @@
         <v>-1.407523</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.229945</v>
+        <v>-1.255369</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.025447</v>
+        <v>-2.04419</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.416521</v>
+        <v>0.408067</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.526134</v>
+        <v>0.499323</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>1.396074</v>
+        <v>1.284874</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>1.973054</v>
+        <v>1.909733</v>
       </c>
     </row>
     <row r="28">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-9.355484000000001</v>
+        <v>-9.680720000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.273834</v>
+        <v>-1.281074</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.193133</v>
@@ -2258,7 +2258,7 @@
         <v>-0.211276</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.041691</v>
+        <v>-0.044734</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-2.611467</v>
@@ -2270,22 +2270,22 @@
         <v>-1.352676</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.127481</v>
+        <v>-1.152905</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.949031</v>
+        <v>-1.967774</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.481408</v>
+        <v>0.472954</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.712105</v>
+        <v>0.685294</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>1.535276</v>
+        <v>1.424076</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>2.221635</v>
+        <v>2.158314</v>
       </c>
     </row>
     <row r="30">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-40.22364155603582</v>
+        <v>-43.15953998147577</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>-1158.700233828351</v>
@@ -2347,22 +2347,22 @@
         <v>-37.4839969008024</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-18.49359692497558</v>
+        <v>-18.91061611041692</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-27.69577646837147</v>
+        <v>-27.96211494033353</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>5.636386520432147</v>
+        <v>5.537406005684296</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>7.10336120991507</v>
+        <v>6.835917198991072</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>8.757205713531484</v>
+        <v>8.12292153573889</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>10.35341276261713</v>
+        <v>10.05831998205611</v>
       </c>
     </row>
     <row r="31">
@@ -2543,13 +2543,13 @@
         <v>0.316047</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.227077</v>
+        <v>0.117075</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.824103</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>3.205914</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.731443</v>
@@ -2669,13 +2669,13 @@
         <v>0.316047</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.227077</v>
+        <v>0.117075</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.824103</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>3.205914</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.731443</v>
@@ -3428,10 +3428,10 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.859892</v>
+        <v>0.035789</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.275157</v>
+        <v>0.069243</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.07895199999999999</v>
@@ -8216,7 +8216,7 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0098</v>
       </c>
       <c r="P124" s="3" t="n">
         <v>0</v>
@@ -8277,7 +8277,7 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0098</v>
       </c>
       <c r="P125" s="3" t="n">
         <v>0</v>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -35400,7 +35400,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -67844,7 +67848,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -75206,7 +75210,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
@@ -82528,7 +82532,7 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E702" s="5" t="n">
@@ -85158,7 +85162,7 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E727" s="5" t="n">

--- a/output/pdf_financials_xlsx/BEW.xlsx
+++ b/output/pdf_financials_xlsx/BEW.xlsx
@@ -790,34 +790,34 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.038484</v>
+        <v>0.066765</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.288958</v>
+        <v>0.366762</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.488917</v>
+        <v>0.62339</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.563385</v>
+        <v>0.740944</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.433066</v>
+        <v>0.646559</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.426388</v>
+        <v>0.5939759999999999</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.495191</v>
+        <v>0.658562</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.565569</v>
+        <v>0.784045</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.862151</v>
+        <v>1.144907</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.411313</v>
+        <v>1.720805</v>
       </c>
     </row>
     <row r="8">
@@ -4664,34 +4664,34 @@
         <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.078566</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.078499</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.048277</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.0906</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.1706</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.1028</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.1501</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.156723</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.1622</v>
       </c>
     </row>
     <row r="68">
@@ -4739,7 +4739,7 @@
         <v>1.329525</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0</v>
+        <v>0.0906</v>
       </c>
       <c r="O68" s="3" t="n">
         <v>1.506549</v>
@@ -5180,7 +5180,7 @@
         <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.909544</v>
+        <v>0.818944</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.013392</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>-0.036613</v>
@@ -7100,7 +7100,7 @@
         <v>0.08032499999999999</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.198573</v>
+        <v>-0.211965</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>0.191309</v>
@@ -7167,28 +7167,28 @@
         <v>0</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0.282699</v>
+        <v>0.757738</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0.19234</v>
+        <v>0.685526</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0.300846</v>
+        <v>0.705552</v>
       </c>
       <c r="N107" s="3" t="n">
         <v>0.00010386</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0.029336</v>
+        <v>0.109901</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0.051229</v>
+        <v>0.139767</v>
       </c>
       <c r="Q107" s="3" t="n">
         <v>0.037309</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>0.071474</v>
+        <v>0.408032</v>
       </c>
       <c r="S107" s="3" t="n">
         <v>0.265084</v>
@@ -7362,19 +7362,19 @@
         <v>0</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.001891</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.002811</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.051379</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.068192</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0</v>
+        <v>0.056281</v>
       </c>
     </row>
     <row r="111">
@@ -7396,7 +7396,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001188</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -7628,13 +7628,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>3.86453</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.839597</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.143043</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -8835,7 +8835,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001188</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -8896,7 +8896,7 @@
         <v>-0.06361600000000001</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.184396</v>
+        <v>-0.185584</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.056212</v>
@@ -28360,7 +28360,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -31168,7 +31172,11 @@
           <t>Share-based compensation expense (Note 15) - - - 71,474</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -31780,7 +31788,11 @@
           <t>Share-based compensation expense (Note 15) - - - 265,084</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -32700,7 +32712,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -33942,7 +33958,11 @@
           <t>Share-based compensation expense (Note 14) - - 51,229 -</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -34362,7 +34382,11 @@
           <t>Share-based compensation expense (Note 14) - - 37,309 -</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -35822,7 +35846,11 @@
           <t>Share-based compensation expense (Note 14) - - 29,336</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -36246,7 +36274,11 @@
           <t>Share-based compensation expense (Note 14) - - 51,229</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -37292,7 +37324,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -37814,7 +37850,11 @@
           <t>Share-based compensation expense (Note 13) - - 300,846</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -38450,7 +38490,11 @@
           <t>Share-based compensation expense (Note 13) - - 103,860</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -39918,7 +39962,11 @@
           <t>Share-based compensation expense (Note 13) - - - 192,340</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -40342,7 +40390,11 @@
           <t>Share-based compensation expense (Note 13) - - - 300,846</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -40660,7 +40712,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -42560,7 +42616,11 @@
           <t>Share-based compensation expense (Note 13) - - - 192,340</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -47428,7 +47488,11 @@
           <t>GST receivables</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
@@ -49214,7 +49278,11 @@
           <t>Gross proceeds from private placement</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -54904,7 +54972,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -61768,7 +61840,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E504" s="5" t="n">
         <v>3.86453</v>
       </c>
@@ -64388,7 +64464,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D529" t="inlineStr"/>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E529" s="5" t="n">
         <v>3.86453</v>
       </c>
@@ -66474,7 +66554,11 @@
           <t>General and office expenses</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr">
         <is>
           <t>-</t>
